--- a/docs/deliverables/데이터정의서.xlsx
+++ b/docs/deliverables/데이터정의서.xlsx
@@ -227,7 +227,7 @@
     <t xml:space="preserve">작성일</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05</t>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">기준</t>
@@ -250,7 +250,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234 — apps/api/prisma/schema.prisma, migrations/*.sql</t>
+      <t xml:space="preserve">8ba23bd — apps/api/prisma/schema.prisma, migrations/*.sql</t>
     </r>
     <r>
       <rPr>

--- a/docs/deliverables/데이터정의서.xlsx
+++ b/docs/deliverables/데이터정의서.xlsx
@@ -237,20 +237,49 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장소 커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8ba23bd — apps/api/prisma/schema.prisma, migrations/*.sql</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(dev </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">브랜치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — apps/api/prisma/schema.prisma, migrations/*.sql</t>
     </r>
     <r>
       <rPr>
@@ -10132,7 +10161,7 @@
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
     </row>

--- a/docs/deliverables/데이터정의서.xlsx
+++ b/docs/deliverables/데이터정의서.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB 규칙" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'컬럼 정의'!$A$4:$K$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'컬럼 정의'!$A$4:$K$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,7 +571,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 저장소(dev 브랜치) — apps/api/prisma/schema.prisma, migrations/*.sql에서 자동 생성</t>
+          <t>2026-10-20 저장소(dev 브랜치) — apps/api/prisma/schema.prisma, migrations/*.sql에서 자동 생성</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>테이블 31개 · 컬럼 264개 · 코드(enum) 24종 · CHECK 18개 · 트리거 7개</t>
+          <t>테이블 32개 · 컬럼 277개 · 코드(enum) 26종 · CHECK 20개 · 트리거 8개</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 신청(StaffProfileChangeRequest), 첨부파일(Attachment), 읽음 확인(PostReadReceipt), 프로그램 시간표 틀(ProgramScheduleTemplate), 혼잡도 기록(CongestionSnapshot), 시설 입퇴장(FacilityCheckIn) — 스키마에만 있고 코드가 읽거나 쓰지 않는다. 사유는 테이블 목록의 설명(요구사항 정의서 "미구현"·"범위 제외" 탭)</t>
+          <t>읽음 확인(PostReadReceipt), 프로그램 시간표 틀(ProgramScheduleTemplate), 혼잡도 기록(CongestionSnapshot), 시설 입퇴장(FacilityCheckIn) — 스키마에만 있고 코드가 읽거나 쓰지 않는다. 사유는 테이블 목록의 설명(요구사항 정의서 "미구현"·"범위 제외" 탭)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -955,16 +955,16 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>직원 본인의 인사정보 변경 신청과 관리자 1단계 승인(D11). 미사용 — 신청·승인 API와 화면이 아직 없다(RFP 미구현)</t>
+          <t>직원 본인의 인사정보 변경 신청과 관리자 1단계 승인(D11, ADR-STF-09)</t>
         </is>
       </c>
       <c r="F10" s="4">
         <f>COUNTIF('컬럼 정의'!$B:$B,C10)</f>
         <v/>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>미사용(설계만)</t>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>본사→현장, 현장→이용자 공지</t>
+          <t>본사→현장, 현장→이용자 공지. 지점 공지는 대상 시설을 지정할 수 있다(게시판 ADR-BRD-05)</t>
         </is>
       </c>
       <c r="F15" s="4">
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>게시글 첨부(교육자료 등). 미사용 — 파일 저장소를 정하지 않아 첨부 API가 없다(RFP 미구현)</t>
+          <t>게시글 첨부(교육자료·이미지 등). 파일은 저장소(Supabase Storage)에 두고 경로만 저장한다(ADR-BRD-04, D57)</t>
         </is>
       </c>
       <c r="F16" s="4">
         <f>COUNTIF('컬럼 정의'!$B:$B,C16)</f>
         <v/>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>미사용(설계만)</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -1722,22 +1722,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>CodeSequence</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>채번 시퀀스</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>지점·종류별 코드(회원번호·직원코드·자산코드) 일련번호</t>
+          <t>지점 관리자가 본사에 올리는 업무지원 요청과 본사의 처리 상태(D56)</t>
         </is>
       </c>
       <c r="F33" s="4">
@@ -1761,17 +1761,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>MemberLinkAttempt</t>
+          <t>CodeSequence</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>회원 연동 시도</t>
+          <t>채번 시퀀스</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>오프라인 회원↔앱 계정 연동 실패 기록(시도 제한용)</t>
+          <t>지점·종류별 코드(회원번호·직원코드·자산코드) 일련번호</t>
         </is>
       </c>
       <c r="F34" s="4">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>MemberLinkAttempt</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>변경 이력</t>
+          <t>회원 연동 시도</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 4종(역할 전환·퇴사·파견 발령·파견 종료)과 관리자의 상세 전화번호 열람을 쓰기와 같은 트랜잭션에서 기록한다(D44·D47). 본사만 조회. 다른 쓰기는 기록하지 않는다</t>
+          <t>오프라인 회원↔앱 계정 연동 실패 기록(시도 제한용)</t>
         </is>
       </c>
       <c r="F35" s="4">
@@ -1819,13 +1819,47 @@
       </c>
     </row>
     <row r="36">
-      <c r="E36" s="8" t="inlineStr">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>변경 이력</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>인사 변경 4종(역할 전환·퇴사·파견 발령·파견 종료)과 관리자의 상세 전화번호 열람을 쓰기와 같은 트랜잭션에서 기록한다(D44·D47). 본사만 조회. 다른 쓰기는 기록하지 않는다</t>
+        </is>
+      </c>
+      <c r="F36" s="4">
+        <f>COUNTIF('컬럼 정의'!$B:$B,C36)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="F36" s="8">
-        <f>SUM(F5:F35)</f>
+      <c r="F37" s="8">
+        <f>SUM(F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -1840,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K268"/>
+  <dimension ref="A1:K281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6378,35 +6412,35 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>viewCount</t>
+          <t>facilityId</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
-      <c r="G107" s="9" t="inlineStr"/>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>Facility.id</t>
+        </is>
+      </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr"/>
       <c r="J107" s="9" t="inlineStr"/>
       <c r="K107" s="9" t="inlineStr">
         <is>
-          <t>조회수</t>
+          <t>게시판 ADR-BRD-05 — 지점 공지(BRANCH_TO_MEMBER)의 대상 시설. null = 지점 전체</t>
         </is>
       </c>
     </row>
@@ -6423,17 +6457,17 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>publishedAt</t>
+          <t>viewCount</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -6443,11 +6477,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I108" s="9" t="inlineStr"/>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J108" s="9" t="inlineStr"/>
       <c r="K108" s="9" t="inlineStr">
         <is>
-          <t>앱이 todayKst()로 채움(파일 상단 날짜 규칙)</t>
+          <t>조회수</t>
         </is>
       </c>
     </row>
@@ -6464,31 +6502,31 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>deletedAt</t>
+          <t>publishedAt</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I109" s="9" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr"/>
       <c r="K109" s="9" t="inlineStr">
         <is>
-          <t>삭제 일시(소프트 삭제)</t>
+          <t>앱이 todayKst()로 채움(파일 상단 날짜 규칙)</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6543,12 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>deletedAt</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -6522,18 +6560,14 @@
       <c r="G110" s="9" t="inlineStr"/>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr"/>
       <c r="J110" s="9" t="inlineStr"/>
       <c r="K110" s="9" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>삭제 일시(소프트 삭제)</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6584,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>updatedAt</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
@@ -6572,62 +6606,58 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>(수정 시 자동)</t>
+          <t>now()</t>
         </is>
       </c>
       <c r="J111" s="9" t="inlineStr"/>
       <c r="K111" s="9" t="inlineStr">
         <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr"/>
+      <c r="G112" s="9" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>(수정 시 자동)</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr"/>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
           <t>수정 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G112" s="4" t="inlineStr"/>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J112" s="4" t="inlineStr"/>
-      <c r="K112" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6674,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>postId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -6657,22 +6687,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>Post.id</t>
-        </is>
-      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>게시글 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6723,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>postId</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -6703,7 +6737,11 @@
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Post.id</t>
+        </is>
+      </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
           <t>N</t>
@@ -6713,7 +6751,7 @@
       <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>파일 주소</t>
+          <t>게시글 ID</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6768,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>fileName</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -6754,7 +6792,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>파일명</t>
+          <t>파일 주소</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6809,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>fileType</t>
+          <t>fileName</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6795,7 +6833,7 @@
       <c r="J116" s="4" t="inlineStr"/>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>파일 형식</t>
+          <t>파일명</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6850,17 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>fileSize</t>
+          <t>fileType</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr"/>
@@ -6836,56 +6874,48 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
+          <t>파일 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>fileSize</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
           <t>파일 크기(byte)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>PostReadReceipt</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J118" s="9" t="inlineStr"/>
-      <c r="K118" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6932,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>postId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -6915,22 +6945,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr"/>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>Post.id</t>
-        </is>
-      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr"/>
       <c r="H119" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I119" s="9" t="inlineStr"/>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J119" s="9" t="inlineStr"/>
       <c r="K119" s="9" t="inlineStr">
         <is>
-          <t>게시글 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6981,7 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>accountId</t>
+          <t>postId</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -6961,7 +6995,11 @@
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
-      <c r="G120" s="9" t="inlineStr"/>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>Post.id</t>
+        </is>
+      </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -6971,7 +7009,7 @@
       <c r="J120" s="9" t="inlineStr"/>
       <c r="K120" s="9" t="inlineStr">
         <is>
-          <t>계정 ID</t>
+          <t>게시글 ID</t>
         </is>
       </c>
     </row>
@@ -6988,17 +7026,17 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>readAt</t>
+          <t>accountId</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -7008,64 +7046,56 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I121" s="9" t="inlineStr"/>
       <c r="J121" s="9" t="inlineStr"/>
       <c r="K121" s="9" t="inlineStr">
         <is>
+          <t>계정 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>PostReadReceipt</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>readAt</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr"/>
+      <c r="G122" s="9" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr"/>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
           <t>열람 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr"/>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J122" s="4" t="inlineStr"/>
-      <c r="K122" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7112,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>accountId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -7095,26 +7125,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="4" t="inlineStr">
-        <is>
-          <t>Account.id</t>
-        </is>
-      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr"/>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>계정 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -7131,12 +7161,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>accountId</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -7147,19 +7177,23 @@
       <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>Branch.id</t>
+          <t>Account.id</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr"/>
-      <c r="J124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>지점 ID</t>
+          <t>계정 ID</t>
         </is>
       </c>
     </row>
@@ -7176,12 +7210,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>assignedStaffId</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -7192,19 +7226,19 @@
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Staff.id</t>
+          <t>Branch.id</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>담당 트레이너 등(선택) — 없으면 회원권만 등록하고 담당 직원이 없는 회원</t>
+          <t>지점 ID</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7255,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>memberNo</t>
+          <t>assignedStaffId</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -7235,21 +7269,21 @@
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>Staff.id</t>
+        </is>
+      </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>회원번호</t>
+          <t>담당 트레이너 등(선택) — 없으면 회원권만 등록하고 담당 직원이 없는 회원</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7300,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>memberNo</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -7287,10 +7321,14 @@
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>회원번호</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7345,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -7324,14 +7362,14 @@
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>연락처</t>
+          <t>이름</t>
         </is>
       </c>
     </row>
@@ -7348,17 +7386,17 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>birthDate</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr"/>
@@ -7372,7 +7410,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>생년월일</t>
+          <t>연락처</t>
         </is>
       </c>
     </row>
@@ -7389,17 +7427,17 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>birthDate</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
@@ -7413,7 +7451,7 @@
       <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>성별</t>
+          <t>생년월일</t>
         </is>
       </c>
     </row>
@@ -7430,31 +7468,31 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>joinedAt</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>앱이 todayKst()로 채움(파일 상단 날짜 규칙)</t>
+          <t>성별</t>
         </is>
       </c>
     </row>
@@ -7471,17 +7509,17 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>joinedAt</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>MemberStatus</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>enum MemberStatus</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
@@ -7491,15 +7529,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
+      <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>상태(코드 정의 참고)</t>
+          <t>앱이 todayKst()로 채움(파일 상단 날짜 규칙)</t>
         </is>
       </c>
     </row>
@@ -7516,17 +7550,17 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>guardianConsent</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>MemberStatus</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum MemberStatus</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
@@ -7538,13 +7572,13 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>미성년 회원 법정대리인 동의 (회원관리 A-3·A-6)</t>
+          <t>상태(코드 정의 참고)</t>
         </is>
       </c>
     </row>
@@ -7561,31 +7595,35 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>memo</t>
+          <t>guardianConsent</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I134" s="4" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>메모</t>
+          <t>미성년 회원 법정대리인 동의 (회원관리 A-3·A-6)</t>
         </is>
       </c>
     </row>
@@ -7602,35 +7640,31 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>memo</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr"/>
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7681,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>updatedAt</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -7669,62 +7703,58 @@
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>(수정 시 자동)</t>
+          <t>now()</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>(수정 시 자동)</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
           <t>수정 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>CourseEnrollment</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="inlineStr"/>
-      <c r="K137" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7771,7 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>memberId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -7754,22 +7784,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F138" s="9" t="inlineStr"/>
-      <c r="G138" s="9" t="inlineStr">
-        <is>
-          <t>Member.id</t>
-        </is>
-      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr"/>
       <c r="H138" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I138" s="9" t="inlineStr"/>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J138" s="9" t="inlineStr"/>
       <c r="K138" s="9" t="inlineStr">
         <is>
-          <t>회원 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7820,7 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>programId</t>
+          <t>memberId</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -7802,7 +7836,7 @@
       <c r="F139" s="9" t="inlineStr"/>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Program.id</t>
+          <t>Member.id</t>
         </is>
       </c>
       <c r="H139" s="9" t="inlineStr">
@@ -7814,7 +7848,7 @@
       <c r="J139" s="9" t="inlineStr"/>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>프로그램 ID</t>
+          <t>회원 ID</t>
         </is>
       </c>
     </row>
@@ -7831,21 +7865,25 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>enrolledAt</t>
+          <t>programId</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr"/>
-      <c r="G140" s="9" t="inlineStr"/>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>Program.id</t>
+        </is>
+      </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -7855,7 +7893,7 @@
       <c r="J140" s="9" t="inlineStr"/>
       <c r="K140" s="9" t="inlineStr">
         <is>
-          <t>수강 등록일</t>
+          <t>프로그램 ID</t>
         </is>
       </c>
     </row>
@@ -7872,12 +7910,12 @@
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>expiresAt</t>
+          <t>enrolledAt</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -7889,14 +7927,14 @@
       <c r="G141" s="9" t="inlineStr"/>
       <c r="H141" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I141" s="9" t="inlineStr"/>
       <c r="J141" s="9" t="inlineStr"/>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>만료 일시</t>
+          <t>수강 등록일</t>
         </is>
       </c>
     </row>
@@ -7913,84 +7951,76 @@
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>expiresAt</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>EnrollmentStatus</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>enum EnrollmentStatus</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr"/>
       <c r="G142" s="9" t="inlineStr"/>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr"/>
       <c r="J142" s="9" t="inlineStr"/>
       <c r="K142" s="9" t="inlineStr">
         <is>
+          <t>만료 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>CourseEnrollment</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>EnrollmentStatus</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>enum EnrollmentStatus</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr"/>
+      <c r="G143" s="9" t="inlineStr"/>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="inlineStr"/>
+      <c r="K143" s="9" t="inlineStr">
+        <is>
           <t>상태(코드 정의 참고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>PTSession</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr"/>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr"/>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8037,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>memberId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -8020,22 +8050,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr"/>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>Member.id</t>
-        </is>
-      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I144" s="4" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>회원 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8086,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>programId</t>
+          <t>memberId</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -8068,7 +8102,7 @@
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Program.id</t>
+          <t>Member.id</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -8080,7 +8114,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>프로그램 ID</t>
+          <t>회원 ID</t>
         </is>
       </c>
     </row>
@@ -8097,21 +8131,25 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>totalSessions</t>
+          <t>programId</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr"/>
-      <c r="G146" s="4" t="inlineStr"/>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>Program.id</t>
+        </is>
+      </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
           <t>N</t>
@@ -8121,7 +8159,7 @@
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>총 세션 수</t>
+          <t>프로그램 ID</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8176,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>usedSessions</t>
+          <t>totalSessions</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -8158,15 +8196,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>사용 세션 수</t>
+          <t>총 세션 수</t>
         </is>
       </c>
     </row>
@@ -8183,17 +8217,17 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>purchasedAt</t>
+          <t>usedSessions</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr"/>
@@ -8203,60 +8237,56 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I148" s="4" t="inlineStr"/>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr">
         <is>
+          <t>사용 세션 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>PTSession</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>purchasedAt</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
           <t>구매 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>PTSessionLog</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr"/>
-      <c r="H149" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J149" s="9" t="inlineStr"/>
-      <c r="K149" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8303,7 @@
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>ptSessionId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -8286,22 +8316,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F150" s="9" t="inlineStr"/>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>PTSession.id</t>
-        </is>
-      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr"/>
       <c r="H150" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I150" s="9" t="inlineStr"/>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J150" s="9" t="inlineStr"/>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>PT 세션권 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8318,35 +8352,35 @@
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>usedAt</t>
+          <t>ptSessionId</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr"/>
-      <c r="G151" s="9" t="inlineStr"/>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>PTSession.id</t>
+        </is>
+      </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I151" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I151" s="9" t="inlineStr"/>
       <c r="J151" s="9" t="inlineStr"/>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>사용 일시</t>
+          <t>PT 세션권 ID</t>
         </is>
       </c>
     </row>
@@ -8363,80 +8397,76 @@
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>usedAt</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp(3)</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr"/>
       <c r="G152" s="9" t="inlineStr"/>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I152" s="9" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J152" s="9" t="inlineStr"/>
       <c r="K152" s="9" t="inlineStr">
         <is>
+          <t>사용 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>PTSessionLog</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>String?</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr"/>
+      <c r="G153" s="9" t="inlineStr"/>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="inlineStr"/>
+      <c r="J153" s="9" t="inlineStr"/>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Instructor</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr"/>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr"/>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8483,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -8466,22 +8496,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F154" s="4" t="inlineStr"/>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>Branch.id</t>
-        </is>
-      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr"/>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>지점 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8532,12 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>staffId</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -8514,23 +8548,19 @@
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Staff.id</t>
+          <t>Branch.id</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>소속 직원이 겸임하는 경우 연결(선택)</t>
+          <t>지점 ID</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8577,12 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>staffId</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -8561,17 +8591,25 @@
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr"/>
-      <c r="G156" s="4" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>Staff.id</t>
+        </is>
+      </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr"/>
-      <c r="J156" s="4" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>소속 직원이 겸임하는 경우 연결(선택)</t>
         </is>
       </c>
     </row>
@@ -8588,12 +8626,12 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -8605,14 +8643,14 @@
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>전문 종목</t>
+          <t>이름</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8667,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>specialty</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -8653,7 +8691,7 @@
       <c r="J158" s="4" t="inlineStr"/>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>소개</t>
+          <t>전문 종목</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8708,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>photoUrl</t>
+          <t>bio</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -8694,7 +8732,7 @@
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>사진 주소</t>
+          <t>소개</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8749,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>photoUrl</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -8735,7 +8773,7 @@
       <c r="J160" s="4" t="inlineStr"/>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>연락처</t>
+          <t>사진 주소</t>
         </is>
       </c>
     </row>
@@ -8752,84 +8790,76 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr">
         <is>
+          <t>연락처</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Instructor</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>isActive</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr"/>
+      <c r="G162" s="4" t="inlineStr"/>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr"/>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
           <t>사용 여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="B162" s="9" t="inlineStr">
-        <is>
-          <t>Program</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D162" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E162" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G162" s="9" t="inlineStr"/>
-      <c r="H162" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I162" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J162" s="9" t="inlineStr"/>
-      <c r="K162" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8876,7 @@
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
@@ -8859,22 +8889,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F163" s="9" t="inlineStr"/>
-      <c r="G163" s="9" t="inlineStr">
-        <is>
-          <t>Branch.id</t>
-        </is>
-      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr"/>
       <c r="H163" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I163" s="9" t="inlineStr"/>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J163" s="9" t="inlineStr"/>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>지점 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -8891,12 +8925,12 @@
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>facilityId</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
@@ -8907,19 +8941,19 @@
       <c r="F164" s="9" t="inlineStr"/>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>Facility.id</t>
+          <t>Branch.id</t>
         </is>
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I164" s="9" t="inlineStr"/>
       <c r="J164" s="9" t="inlineStr"/>
       <c r="K164" s="9" t="inlineStr">
         <is>
-          <t>시설 ID</t>
+          <t>지점 ID</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8970,7 @@
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>instructorId</t>
+          <t>facilityId</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
@@ -8952,7 +8986,7 @@
       <c r="F165" s="9" t="inlineStr"/>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>Instructor.id</t>
+          <t>Facility.id</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr">
@@ -8964,7 +8998,7 @@
       <c r="J165" s="9" t="inlineStr"/>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>강사 ID</t>
+          <t>시설 ID</t>
         </is>
       </c>
     </row>
@@ -8981,12 +9015,12 @@
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>instructorId</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
@@ -8995,17 +9029,21 @@
         </is>
       </c>
       <c r="F166" s="9" t="inlineStr"/>
-      <c r="G166" s="9" t="inlineStr"/>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>Instructor.id</t>
+        </is>
+      </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I166" s="9" t="inlineStr"/>
       <c r="J166" s="9" t="inlineStr"/>
       <c r="K166" s="9" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>강사 ID</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9060,7 @@
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
@@ -9046,7 +9084,7 @@
       <c r="J167" s="9" t="inlineStr"/>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>종목: 헬스/수영/골프/요가/독서실이용 등</t>
+          <t>이름</t>
         </is>
       </c>
     </row>
@@ -9063,17 +9101,17 @@
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>ageGroup</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>AgeGroup</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>enum AgeGroup</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr"/>
@@ -9083,15 +9121,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I168" s="9" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
+      <c r="I168" s="9" t="inlineStr"/>
       <c r="J168" s="9" t="inlineStr"/>
       <c r="K168" s="9" t="inlineStr">
         <is>
-          <t>대상 연령대</t>
+          <t>종목: 헬스/수영/골프/요가/독서실이용 등</t>
         </is>
       </c>
     </row>
@@ -9108,31 +9142,35 @@
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>ageGroup</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>AgeGroup</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>enum AgeGroup</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr"/>
       <c r="G169" s="9" t="inlineStr"/>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I169" s="9" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
       <c r="J169" s="9" t="inlineStr"/>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>대상 연령대</t>
         </is>
       </c>
     </row>
@@ -9149,35 +9187,31 @@
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr"/>
       <c r="G170" s="9" t="inlineStr"/>
       <c r="H170" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I170" s="9" t="inlineStr"/>
       <c r="J170" s="9" t="inlineStr"/>
       <c r="K170" s="9" t="inlineStr">
         <is>
-          <t>가격(원)</t>
+          <t>설명</t>
         </is>
       </c>
     </row>
@@ -9194,17 +9228,17 @@
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>pricingType</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>PricingType</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>enum PricingType</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr"/>
@@ -9214,11 +9248,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I171" s="9" t="inlineStr"/>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J171" s="9" t="inlineStr"/>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>이용 방식</t>
+          <t>가격(원)</t>
         </is>
       </c>
     </row>
@@ -9235,31 +9273,31 @@
       </c>
       <c r="C172" s="9" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>pricingType</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Int?</t>
+          <t>PricingType</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum PricingType</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr"/>
       <c r="G172" s="9" t="inlineStr"/>
       <c r="H172" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I172" s="9" t="inlineStr"/>
       <c r="J172" s="9" t="inlineStr"/>
       <c r="K172" s="9" t="inlineStr">
         <is>
-          <t>정원</t>
+          <t>이용 방식</t>
         </is>
       </c>
     </row>
@@ -9276,35 +9314,31 @@
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>ProgramStatus</t>
+          <t>Int?</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>enum ProgramStatus</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr"/>
       <c r="G173" s="9" t="inlineStr"/>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>PREPARING</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I173" s="9" t="inlineStr"/>
       <c r="J173" s="9" t="inlineStr"/>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>지점별 "진행중" 파악의 핵심 필드 — 강사프로그램게시 A-3 §3-2 참고</t>
+          <t>정원</t>
         </is>
       </c>
     </row>
@@ -9321,17 +9355,17 @@
       </c>
       <c r="C174" s="9" t="inlineStr">
         <is>
-          <t>startDate</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>ProgramStatus</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>enum ProgramStatus</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr"/>
@@ -9341,11 +9375,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I174" s="9" t="inlineStr"/>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>PREPARING</t>
+        </is>
+      </c>
       <c r="J174" s="9" t="inlineStr"/>
       <c r="K174" s="9" t="inlineStr">
         <is>
-          <t>모집/개강일</t>
+          <t>지점별 "진행중" 파악의 핵심 필드 — 강사프로그램게시 A-3 §3-2 참고</t>
         </is>
       </c>
     </row>
@@ -9362,12 +9400,12 @@
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>endDate</t>
+          <t>startDate</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
@@ -9379,14 +9417,14 @@
       <c r="G175" s="9" t="inlineStr"/>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I175" s="9" t="inlineStr"/>
       <c r="J175" s="9" t="inlineStr"/>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>종료 예정일(상시 운영이면 null)</t>
+          <t>모집/개강일</t>
         </is>
       </c>
     </row>
@@ -9403,35 +9441,31 @@
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>endDate</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr"/>
       <c r="G176" s="9" t="inlineStr"/>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I176" s="9" t="inlineStr"/>
       <c r="J176" s="9" t="inlineStr"/>
       <c r="K176" s="9" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>종료 예정일(상시 운영이면 null)</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9482,7 @@
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>updatedAt</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
@@ -9470,62 +9504,58 @@
       </c>
       <c r="I177" s="9" t="inlineStr">
         <is>
-          <t>(수정 시 자동)</t>
+          <t>now()</t>
         </is>
       </c>
       <c r="J177" s="9" t="inlineStr"/>
       <c r="K177" s="9" t="inlineStr">
         <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr"/>
+      <c r="G178" s="9" t="inlineStr"/>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>(수정 시 자동)</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="inlineStr"/>
+      <c r="K178" s="9" t="inlineStr">
+        <is>
           <t>수정 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>ProgramScheduleTemplate</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr"/>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr"/>
-      <c r="K178" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9572,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>programId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -9555,22 +9585,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F179" s="4" t="inlineStr"/>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>Program.id</t>
-        </is>
-      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>프로그램 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -9587,21 +9621,25 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>dayOfWeek</t>
+          <t>programId</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr"/>
-      <c r="G180" s="4" t="inlineStr"/>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>Program.id</t>
+        </is>
+      </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
           <t>N</t>
@@ -9611,7 +9649,7 @@
       <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>0(일)~6(토)</t>
+          <t>프로그램 ID</t>
         </is>
       </c>
     </row>
@@ -9628,17 +9666,17 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>dayOfWeek</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr"/>
@@ -9652,7 +9690,7 @@
       <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>"HH:mm"</t>
+          <t>0(일)~6(토)</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9707,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>startTime</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -9693,56 +9731,48 @@
       <c r="J182" s="4" t="inlineStr"/>
       <c r="K182" s="4" t="inlineStr">
         <is>
+          <t>"HH:mm"</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>ProgramScheduleTemplate</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr"/>
+      <c r="G183" s="4" t="inlineStr"/>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr"/>
+      <c r="J183" s="4" t="inlineStr"/>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
           <t>종료 시각(HH:mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
-        <is>
-          <t>ScheduleSlot</t>
-        </is>
-      </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E183" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I183" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J183" s="9" t="inlineStr"/>
-      <c r="K183" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9789,7 @@
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>programId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
@@ -9772,22 +9802,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F184" s="9" t="inlineStr"/>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>Program.id</t>
-        </is>
-      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr"/>
       <c r="H184" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I184" s="9" t="inlineStr"/>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J184" s="9" t="inlineStr"/>
       <c r="K184" s="9" t="inlineStr">
         <is>
-          <t>프로그램 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -9804,21 +9838,25 @@
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>programId</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr"/>
-      <c r="G185" s="9" t="inlineStr"/>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>Program.id</t>
+        </is>
+      </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -9828,7 +9866,7 @@
       <c r="J185" s="9" t="inlineStr"/>
       <c r="K185" s="9" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>프로그램 ID</t>
         </is>
       </c>
     </row>
@@ -9845,17 +9883,17 @@
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F186" s="9" t="inlineStr"/>
@@ -9869,7 +9907,7 @@
       <c r="J186" s="9" t="inlineStr"/>
       <c r="K186" s="9" t="inlineStr">
         <is>
-          <t>시작 시각(HH:mm)</t>
+          <t>날짜</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9924,7 @@
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>startTime</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
@@ -9910,7 +9948,7 @@
       <c r="J187" s="9" t="inlineStr"/>
       <c r="K187" s="9" t="inlineStr">
         <is>
-          <t>종료 시각(HH:mm)</t>
+          <t>시작 시각(HH:mm)</t>
         </is>
       </c>
     </row>
@@ -9927,17 +9965,17 @@
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>endTime</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr"/>
@@ -9951,56 +9989,48 @@
       <c r="J188" s="9" t="inlineStr"/>
       <c r="K188" s="9" t="inlineStr">
         <is>
+          <t>종료 시각(HH:mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>ScheduleSlot</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr"/>
+      <c r="G189" s="9" t="inlineStr"/>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I189" s="9" t="inlineStr"/>
+      <c r="J189" s="9" t="inlineStr"/>
+      <c r="K189" s="9" t="inlineStr">
+        <is>
           <t>정원</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>Reservation</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr"/>
-      <c r="H189" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J189" s="4" t="inlineStr"/>
-      <c r="K189" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10047,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>memberId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -10030,22 +10060,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr"/>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t>Member.id</t>
-        </is>
-      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr"/>
       <c r="H190" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J190" s="4" t="inlineStr"/>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>회원 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10096,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>scheduleSlotId</t>
+          <t>memberId</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -10078,7 +10112,7 @@
       <c r="F191" s="4" t="inlineStr"/>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>ScheduleSlot.id</t>
+          <t>Member.id</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -10090,7 +10124,7 @@
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>회차 ID</t>
+          <t>회원 ID</t>
         </is>
       </c>
     </row>
@@ -10107,35 +10141,35 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>scheduleSlotId</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>ReservationStatus</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>enum ReservationStatus</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr"/>
-      <c r="G192" s="4" t="inlineStr"/>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>ScheduleSlot.id</t>
+        </is>
+      </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr">
-        <is>
-          <t>REQUESTED</t>
-        </is>
-      </c>
+      <c r="I192" s="4" t="inlineStr"/>
       <c r="J192" s="4" t="inlineStr"/>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>상태(코드 정의 참고)</t>
+          <t>회차 ID</t>
         </is>
       </c>
     </row>
@@ -10152,17 +10186,17 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>ReservationStatus</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>enum ReservationStatus</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr"/>
@@ -10174,13 +10208,13 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>REQUESTED</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>상태(코드 정의 참고)</t>
         </is>
       </c>
     </row>
@@ -10197,12 +10231,12 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>cancelledAt</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -10214,14 +10248,18 @@
       <c r="G194" s="4" t="inlineStr"/>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J194" s="4" t="inlineStr"/>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>취소 일시</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
@@ -10238,17 +10276,17 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>cancelReason</t>
+          <t>cancelledAt</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp(3)</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr"/>
@@ -10262,56 +10300,48 @@
       <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
+          <t>취소 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Reservation</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>cancelReason</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>String?</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="inlineStr"/>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr"/>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
           <t>취소 사유</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E196" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F196" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr"/>
-      <c r="H196" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I196" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J196" s="9" t="inlineStr"/>
-      <c r="K196" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10358,7 @@
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>reservationId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
@@ -10341,26 +10371,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F197" s="9" t="inlineStr"/>
-      <c r="G197" s="9" t="inlineStr">
-        <is>
-          <t>Reservation.id</t>
-        </is>
-      </c>
+      <c r="F197" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G197" s="9" t="inlineStr"/>
       <c r="H197" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I197" s="9" t="inlineStr"/>
-      <c r="J197" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I197" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="inlineStr"/>
       <c r="K197" s="9" t="inlineStr">
         <is>
-          <t>예약 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10407,7 @@
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>memberId</t>
+          <t>reservationId</t>
         </is>
       </c>
       <c r="D198" s="9" t="inlineStr">
@@ -10393,7 +10423,7 @@
       <c r="F198" s="9" t="inlineStr"/>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>Member.id</t>
+          <t>Reservation.id</t>
         </is>
       </c>
       <c r="H198" s="9" t="inlineStr">
@@ -10402,10 +10432,14 @@
         </is>
       </c>
       <c r="I198" s="9" t="inlineStr"/>
-      <c r="J198" s="9" t="inlineStr"/>
+      <c r="J198" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K198" s="9" t="inlineStr">
         <is>
-          <t>회원 ID</t>
+          <t>예약 ID</t>
         </is>
       </c>
     </row>
@@ -10422,21 +10456,25 @@
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>memberId</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F199" s="9" t="inlineStr"/>
-      <c r="G199" s="9" t="inlineStr"/>
+      <c r="G199" s="9" t="inlineStr">
+        <is>
+          <t>Member.id</t>
+        </is>
+      </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -10446,7 +10484,7 @@
       <c r="J199" s="9" t="inlineStr"/>
       <c r="K199" s="9" t="inlineStr">
         <is>
-          <t>결제 금액(원, 부가세 포함)</t>
+          <t>회원 ID</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10501,7 @@
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>supplyAmount</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
@@ -10487,7 +10525,7 @@
       <c r="J200" s="9" t="inlineStr"/>
       <c r="K200" s="9" t="inlineStr">
         <is>
-          <t>공급가액 = round(amount / 1.1)</t>
+          <t>결제 금액(원, 부가세 포함)</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10542,7 @@
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>vat</t>
+          <t>supplyAmount</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
@@ -10528,7 +10566,7 @@
       <c r="J201" s="9" t="inlineStr"/>
       <c r="K201" s="9" t="inlineStr">
         <is>
-          <t>부가세 = amount - supplyAmount</t>
+          <t>공급가액 = round(amount / 1.1)</t>
         </is>
       </c>
     </row>
@@ -10545,17 +10583,17 @@
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>vat</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>enum PaymentMethod</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr"/>
@@ -10569,7 +10607,7 @@
       <c r="J202" s="9" t="inlineStr"/>
       <c r="K202" s="9" t="inlineStr">
         <is>
-          <t>결제 수단</t>
+          <t>부가세 = amount - supplyAmount</t>
         </is>
       </c>
     </row>
@@ -10586,17 +10624,17 @@
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>method</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>PaymentStatus</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>enum PaymentStatus</t>
+          <t>enum PaymentMethod</t>
         </is>
       </c>
       <c r="F203" s="9" t="inlineStr"/>
@@ -10606,15 +10644,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I203" s="9" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+      <c r="I203" s="9" t="inlineStr"/>
       <c r="J203" s="9" t="inlineStr"/>
       <c r="K203" s="9" t="inlineStr">
         <is>
-          <t>상태(코드 정의 참고)</t>
+          <t>결제 수단</t>
         </is>
       </c>
     </row>
@@ -10631,31 +10665,35 @@
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>mockApprovalNo</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>PaymentStatus</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>enum PaymentStatus</t>
         </is>
       </c>
       <c r="F204" s="9" t="inlineStr"/>
       <c r="G204" s="9" t="inlineStr"/>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I204" s="9" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I204" s="9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="J204" s="9" t="inlineStr"/>
       <c r="K204" s="9" t="inlineStr">
         <is>
-          <t>모의 승인번호</t>
+          <t>상태(코드 정의 참고)</t>
         </is>
       </c>
     </row>
@@ -10672,17 +10710,17 @@
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>approvedAt</t>
+          <t>mockApprovalNo</t>
         </is>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr"/>
@@ -10696,7 +10734,7 @@
       <c r="J205" s="9" t="inlineStr"/>
       <c r="K205" s="9" t="inlineStr">
         <is>
-          <t>승인 일시</t>
+          <t>모의 승인번호</t>
         </is>
       </c>
     </row>
@@ -10713,7 +10751,7 @@
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>refundedAt</t>
+          <t>approvedAt</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
@@ -10737,7 +10775,7 @@
       <c r="J206" s="9" t="inlineStr"/>
       <c r="K206" s="9" t="inlineStr">
         <is>
-          <t>환불 일시</t>
+          <t>승인 일시</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10792,12 @@
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>refundedAt</t>
         </is>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E207" s="9" t="inlineStr">
@@ -10771,67 +10809,59 @@
       <c r="G207" s="9" t="inlineStr"/>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I207" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I207" s="9" t="inlineStr"/>
       <c r="J207" s="9" t="inlineStr"/>
       <c r="K207" s="9" t="inlineStr">
         <is>
+          <t>환불 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="B208" s="9" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>createdAt</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E208" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="inlineStr"/>
+      <c r="G208" s="9" t="inlineStr"/>
+      <c r="H208" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I208" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J208" s="9" t="inlineStr"/>
+      <c r="K208" s="9" t="inlineStr">
+        <is>
           <t>생성 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G208" s="4" t="inlineStr"/>
-      <c r="H208" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I208" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J208" s="4" t="inlineStr"/>
-      <c r="K208" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10878,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -10861,22 +10891,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F209" s="4" t="inlineStr"/>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>Branch.id</t>
-        </is>
-      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr"/>
       <c r="H209" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I209" s="4" t="inlineStr"/>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J209" s="4" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>지점 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10927,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -10907,7 +10941,11 @@
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr"/>
-      <c r="G210" s="4" t="inlineStr"/>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>Branch.id</t>
+        </is>
+      </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
           <t>N</t>
@@ -10917,7 +10955,7 @@
       <c r="J210" s="4" t="inlineStr"/>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>지점 ID</t>
         </is>
       </c>
     </row>
@@ -10934,17 +10972,17 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>FacilityType</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>enum FacilityType</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr"/>
@@ -10958,7 +10996,7 @@
       <c r="J211" s="4" t="inlineStr"/>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>유형</t>
+          <t>이름</t>
         </is>
       </c>
     </row>
@@ -10975,17 +11013,17 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>FacilityType</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum FacilityType</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr"/>
@@ -10999,7 +11037,7 @@
       <c r="J212" s="4" t="inlineStr"/>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>정원</t>
+          <t>유형</t>
         </is>
       </c>
     </row>
@@ -11016,17 +11054,17 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr"/>
@@ -11036,15 +11074,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I213" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="I213" s="4" t="inlineStr"/>
       <c r="J213" s="4" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>사용 여부</t>
+          <t>정원</t>
         </is>
       </c>
     </row>
@@ -11061,17 +11095,17 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>currentCount</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr"/>
@@ -11083,13 +11117,13 @@
       </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J214" s="4" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>현재 인원</t>
+          <t>사용 여부</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11140,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>currentCount</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -11128,13 +11162,13 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>1~5</t>
+          <t>현재 인원</t>
         </is>
       </c>
     </row>
@@ -11151,80 +11185,76 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>lastUpdatedAt</t>
+          <t>level</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr"/>
       <c r="G216" s="4" t="inlineStr"/>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J216" s="4" t="inlineStr"/>
       <c r="K216" s="4" t="inlineStr">
         <is>
+          <t>1~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>lastUpdatedAt</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>DateTime?</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F217" s="4" t="inlineStr"/>
+      <c r="G217" s="4" t="inlineStr"/>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr"/>
+      <c r="J217" s="4" t="inlineStr"/>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
           <t>혼잡도 갱신 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="9" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="B217" s="9" t="inlineStr">
-        <is>
-          <t>CongestionSnapshot</t>
-        </is>
-      </c>
-      <c r="C217" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D217" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E217" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F217" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G217" s="9" t="inlineStr"/>
-      <c r="H217" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I217" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J217" s="9" t="inlineStr"/>
-      <c r="K217" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11271,7 @@
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>facilityId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
@@ -11254,22 +11284,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F218" s="9" t="inlineStr"/>
-      <c r="G218" s="9" t="inlineStr">
-        <is>
-          <t>Facility.id</t>
-        </is>
-      </c>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G218" s="9" t="inlineStr"/>
       <c r="H218" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I218" s="9" t="inlineStr"/>
+      <c r="I218" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J218" s="9" t="inlineStr"/>
       <c r="K218" s="9" t="inlineStr">
         <is>
-          <t>시설 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -11286,21 +11320,25 @@
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>currentCount</t>
+          <t>facilityId</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr"/>
-      <c r="G219" s="9" t="inlineStr"/>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>Facility.id</t>
+        </is>
+      </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -11310,7 +11348,7 @@
       <c r="J219" s="9" t="inlineStr"/>
       <c r="K219" s="9" t="inlineStr">
         <is>
-          <t>현재 인원</t>
+          <t>시설 ID</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11365,7 @@
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>currentCount</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
@@ -11351,7 +11389,7 @@
       <c r="J220" s="9" t="inlineStr"/>
       <c r="K220" s="9" t="inlineStr">
         <is>
-          <t>정원</t>
+          <t>현재 인원</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11406,7 @@
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
@@ -11392,7 +11430,7 @@
       <c r="J221" s="9" t="inlineStr"/>
       <c r="K221" s="9" t="inlineStr">
         <is>
-          <t>1~5</t>
+          <t>정원</t>
         </is>
       </c>
     </row>
@@ -11409,17 +11447,17 @@
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>level</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>CongestionSource</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>enum CongestionSource</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr"/>
@@ -11433,7 +11471,7 @@
       <c r="J222" s="9" t="inlineStr"/>
       <c r="K222" s="9" t="inlineStr">
         <is>
-          <t>기록 출처</t>
+          <t>1~5</t>
         </is>
       </c>
     </row>
@@ -11450,17 +11488,17 @@
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>recordedAt</t>
+          <t>source</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>CongestionSource</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>enum CongestionSource</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr"/>
@@ -11470,64 +11508,56 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I223" s="9" t="inlineStr"/>
       <c r="J223" s="9" t="inlineStr"/>
       <c r="K223" s="9" t="inlineStr">
         <is>
+          <t>기록 출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="inlineStr">
+        <is>
+          <t>CongestionSnapshot</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>recordedAt</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E224" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="inlineStr"/>
+      <c r="G224" s="9" t="inlineStr"/>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I224" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J224" s="9" t="inlineStr"/>
+      <c r="K224" s="9" t="inlineStr">
+        <is>
           <t>기록 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>FacilityCheckIn</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G224" s="4" t="inlineStr"/>
-      <c r="H224" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J224" s="4" t="inlineStr"/>
-      <c r="K224" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11574,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>facilityId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -11557,22 +11587,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr"/>
-      <c r="G225" s="4" t="inlineStr">
-        <is>
-          <t>Facility.id</t>
-        </is>
-      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr"/>
       <c r="H225" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I225" s="4" t="inlineStr"/>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J225" s="4" t="inlineStr"/>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>시설 ID</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11623,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>memberId</t>
+          <t>facilityId</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -11605,7 +11639,7 @@
       <c r="F226" s="4" t="inlineStr"/>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>Member.id</t>
+          <t>Facility.id</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -11617,7 +11651,7 @@
       <c r="J226" s="4" t="inlineStr"/>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>회원 ID</t>
+          <t>시설 ID</t>
         </is>
       </c>
     </row>
@@ -11634,35 +11668,35 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>checkInAt</t>
+          <t>memberId</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr"/>
-      <c r="G227" s="4" t="inlineStr"/>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>Member.id</t>
+        </is>
+      </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I227" s="4" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I227" s="4" t="inlineStr"/>
       <c r="J227" s="4" t="inlineStr"/>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>체크인 일시</t>
+          <t>회원 ID</t>
         </is>
       </c>
     </row>
@@ -11679,12 +11713,12 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>checkOutAt</t>
+          <t>checkInAt</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
@@ -11696,63 +11730,59 @@
       <c r="G228" s="4" t="inlineStr"/>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J228" s="4" t="inlineStr"/>
       <c r="K228" s="4" t="inlineStr">
         <is>
+          <t>체크인 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>FacilityCheckIn</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>checkOutAt</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>DateTime?</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr"/>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr"/>
+      <c r="J229" s="4" t="inlineStr"/>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
           <t>체크아웃 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="9" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="B229" s="9" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="C229" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E229" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F229" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G229" s="9" t="inlineStr"/>
-      <c r="H229" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I229" s="9" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J229" s="9" t="inlineStr"/>
-      <c r="K229" s="9" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -11769,7 +11799,7 @@
       </c>
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t>assetCode</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
@@ -11782,22 +11812,26 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F230" s="9" t="inlineStr"/>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G230" s="9" t="inlineStr"/>
       <c r="H230" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I230" s="9" t="inlineStr"/>
-      <c r="J230" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
+      <c r="J230" s="9" t="inlineStr"/>
       <c r="K230" s="9" t="inlineStr">
         <is>
-          <t>{지점코드}-A{순번}</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11848,7 @@
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>assetCode</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
@@ -11828,21 +11862,21 @@
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr"/>
-      <c r="G231" s="9" t="inlineStr">
-        <is>
-          <t>Branch.id</t>
-        </is>
-      </c>
+      <c r="G231" s="9" t="inlineStr"/>
       <c r="H231" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
       <c r="I231" s="9" t="inlineStr"/>
-      <c r="J231" s="9" t="inlineStr"/>
+      <c r="J231" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="K231" s="9" t="inlineStr">
         <is>
-          <t>지점 ID</t>
+          <t>{지점코드}-A{순번}</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11893,7 @@
       </c>
       <c r="C232" s="9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
@@ -11873,7 +11907,11 @@
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr"/>
-      <c r="G232" s="9" t="inlineStr"/>
+      <c r="G232" s="9" t="inlineStr">
+        <is>
+          <t>Branch.id</t>
+        </is>
+      </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -11883,7 +11921,7 @@
       <c r="J232" s="9" t="inlineStr"/>
       <c r="K232" s="9" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>지점 ID</t>
         </is>
       </c>
     </row>
@@ -11900,17 +11938,17 @@
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>AssetCategory</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>enum AssetCategory</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr"/>
@@ -11924,7 +11962,7 @@
       <c r="J233" s="9" t="inlineStr"/>
       <c r="K233" s="9" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>이름</t>
         </is>
       </c>
     </row>
@@ -11941,17 +11979,17 @@
       </c>
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t>assetType</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>AssetType</t>
+          <t>AssetCategory</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>enum AssetType</t>
+          <t>enum AssetCategory</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr"/>
@@ -11965,7 +12003,7 @@
       <c r="J234" s="9" t="inlineStr"/>
       <c r="K234" s="9" t="inlineStr">
         <is>
-          <t>자산 유형</t>
+          <t>분류</t>
         </is>
       </c>
     </row>
@@ -11982,17 +12020,17 @@
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>acquiredAt</t>
+          <t>assetType</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>AssetType</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>enum AssetType</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr"/>
@@ -12006,7 +12044,7 @@
       <c r="J235" s="9" t="inlineStr"/>
       <c r="K235" s="9" t="inlineStr">
         <is>
-          <t>취득일</t>
+          <t>자산 유형</t>
         </is>
       </c>
     </row>
@@ -12023,17 +12061,17 @@
       </c>
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t>acquisitionCost</t>
+          <t>acquiredAt</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr"/>
@@ -12047,7 +12085,7 @@
       <c r="J236" s="9" t="inlineStr"/>
       <c r="K236" s="9" t="inlineStr">
         <is>
-          <t>취득가액(원)</t>
+          <t>취득일</t>
         </is>
       </c>
     </row>
@@ -12064,12 +12102,12 @@
       </c>
       <c r="C237" s="9" t="inlineStr">
         <is>
-          <t>usefulLifeYears</t>
+          <t>acquisitionCost</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Int?</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
@@ -12081,14 +12119,14 @@
       <c r="G237" s="9" t="inlineStr"/>
       <c r="H237" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I237" s="9" t="inlineStr"/>
       <c r="J237" s="9" t="inlineStr"/>
       <c r="K237" s="9" t="inlineStr">
         <is>
-          <t>FIXED_ASSET만 사용</t>
+          <t>취득가액(원)</t>
         </is>
       </c>
     </row>
@@ -12105,31 +12143,31 @@
       </c>
       <c r="C238" s="9" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>usefulLifeYears</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>AssetStatus</t>
+          <t>Int?</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>enum AssetStatus</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr"/>
       <c r="G238" s="9" t="inlineStr"/>
       <c r="H238" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I238" s="9" t="inlineStr"/>
       <c r="J238" s="9" t="inlineStr"/>
       <c r="K238" s="9" t="inlineStr">
         <is>
-          <t>상태(코드 정의 참고)</t>
+          <t>FIXED_ASSET만 사용</t>
         </is>
       </c>
     </row>
@@ -12146,17 +12184,17 @@
       </c>
       <c r="C239" s="9" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>AssetStatus</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum AssetStatus</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr"/>
@@ -12170,7 +12208,7 @@
       <c r="J239" s="9" t="inlineStr"/>
       <c r="K239" s="9" t="inlineStr">
         <is>
-          <t>CONSUMABLE은 재고 수량, FIXED_ASSET은 항상 1</t>
+          <t>상태(코드 정의 참고)</t>
         </is>
       </c>
     </row>
@@ -12187,31 +12225,31 @@
       </c>
       <c r="C240" s="9" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr"/>
       <c r="G240" s="9" t="inlineStr"/>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I240" s="9" t="inlineStr"/>
       <c r="J240" s="9" t="inlineStr"/>
       <c r="K240" s="9" t="inlineStr">
         <is>
-          <t>보관 위치</t>
+          <t>CONSUMABLE은 재고 수량, FIXED_ASSET은 항상 1</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12266,7 @@
       </c>
       <c r="C241" s="9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
@@ -12252,56 +12290,48 @@
       <c r="J241" s="9" t="inlineStr"/>
       <c r="K241" s="9" t="inlineStr">
         <is>
+          <t>보관 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
+        <is>
+          <t>String?</t>
+        </is>
+      </c>
+      <c r="E242" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="inlineStr"/>
+      <c r="G242" s="9" t="inlineStr"/>
+      <c r="H242" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I242" s="9" t="inlineStr"/>
+      <c r="J242" s="9" t="inlineStr"/>
+      <c r="K242" s="9" t="inlineStr">
+        <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>Document</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F242" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G242" s="4" t="inlineStr"/>
-      <c r="H242" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J242" s="4" t="inlineStr"/>
-      <c r="K242" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -12318,31 +12348,39 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>DocumentCategory</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>enum DocumentCategory</t>
-        </is>
-      </c>
-      <c r="F243" s="4" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G243" s="4" t="inlineStr"/>
       <c r="H243" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I243" s="4" t="inlineStr"/>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J243" s="4" t="inlineStr"/>
       <c r="K243" s="4" t="inlineStr">
         <is>
-          <t>분류</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
@@ -12359,35 +12397,31 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>DocumentCategory</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>enum DocumentCategory</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr"/>
-      <c r="G244" s="4" t="inlineStr">
-        <is>
-          <t>Branch.id</t>
-        </is>
-      </c>
+      <c r="G244" s="4" t="inlineStr"/>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr"/>
       <c r="J244" s="4" t="inlineStr"/>
       <c r="K244" s="4" t="inlineStr">
         <is>
-          <t>전사 문서면 null</t>
+          <t>분류</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12438,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>relatedStaffId</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -12420,7 +12454,7 @@
       <c r="F245" s="4" t="inlineStr"/>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>Staff.id</t>
+          <t>Branch.id</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -12432,7 +12466,7 @@
       <c r="J245" s="4" t="inlineStr"/>
       <c r="K245" s="4" t="inlineStr">
         <is>
-          <t>HR_RECORD 대상 직원</t>
+          <t>전사 문서면 null</t>
         </is>
       </c>
     </row>
@@ -12449,12 +12483,12 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>relatedStaffId</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -12463,17 +12497,21 @@
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr"/>
-      <c r="G246" s="4" t="inlineStr"/>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>Staff.id</t>
+        </is>
+      </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I246" s="4" t="inlineStr"/>
       <c r="J246" s="4" t="inlineStr"/>
       <c r="K246" s="4" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>HR_RECORD 대상 직원</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12528,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>fileUrl</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -12514,7 +12552,7 @@
       <c r="J247" s="4" t="inlineStr"/>
       <c r="K247" s="4" t="inlineStr">
         <is>
-          <t>실제 파일 업로드 인프라는 아직 없음 — 문자열 필드일 뿐</t>
+          <t>제목</t>
         </is>
       </c>
     </row>
@@ -12531,12 +12569,12 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>fileType</t>
+          <t>fileUrl</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>String?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -12548,14 +12586,14 @@
       <c r="G248" s="4" t="inlineStr"/>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr"/>
       <c r="J248" s="4" t="inlineStr"/>
       <c r="K248" s="4" t="inlineStr">
         <is>
-          <t>파일 형식</t>
+          <t>실제 파일 업로드 인프라는 아직 없음 — 문자열 필드일 뿐</t>
         </is>
       </c>
     </row>
@@ -12572,17 +12610,17 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>fileSize</t>
+          <t>fileType</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Int?</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr"/>
@@ -12596,7 +12634,7 @@
       <c r="J249" s="4" t="inlineStr"/>
       <c r="K249" s="4" t="inlineStr">
         <is>
-          <t>파일 크기(byte)</t>
+          <t>파일 형식</t>
         </is>
       </c>
     </row>
@@ -12613,35 +12651,31 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>uploadedBy</t>
+          <t>fileSize</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Int?</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr"/>
-      <c r="G250" s="4" t="inlineStr">
-        <is>
-          <t>Account.id</t>
-        </is>
-      </c>
+      <c r="G250" s="4" t="inlineStr"/>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr"/>
       <c r="J250" s="4" t="inlineStr"/>
       <c r="K250" s="4" t="inlineStr">
         <is>
-          <t>FK → Account(log/093)</t>
+          <t>파일 크기(byte)</t>
         </is>
       </c>
     </row>
@@ -12658,31 +12692,35 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>retentionUntil</t>
+          <t>uploadedBy</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr"/>
-      <c r="G251" s="4" t="inlineStr"/>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>Account.id</t>
+        </is>
+      </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr"/>
       <c r="J251" s="4" t="inlineStr"/>
       <c r="K251" s="4" t="inlineStr">
         <is>
-          <t>null = 영구 보관</t>
+          <t>FK → Account(log/093)</t>
         </is>
       </c>
     </row>
@@ -12699,35 +12737,31 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>retentionUntil</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>timestamp(3)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr"/>
       <c r="G252" s="4" t="inlineStr"/>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I252" s="4" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr"/>
       <c r="J252" s="4" t="inlineStr"/>
       <c r="K252" s="4" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>null = 영구 보관</t>
         </is>
       </c>
     </row>
@@ -12744,12 +12778,12 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>deletedAt</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -12761,117 +12795,125 @@
       <c r="G253" s="4" t="inlineStr"/>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I253" s="4" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J253" s="4" t="inlineStr"/>
       <c r="K253" s="4" t="inlineStr">
         <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>deletedAt</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>DateTime?</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr"/>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr"/>
+      <c r="J254" s="4" t="inlineStr"/>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
           <t>소프트 삭제(D9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="9" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="B254" s="9" t="inlineStr">
-        <is>
-          <t>CodeSequence</t>
-        </is>
-      </c>
-      <c r="C254" s="9" t="inlineStr">
-        <is>
-          <t>branchId</t>
-        </is>
-      </c>
-      <c r="D254" s="9" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E254" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F254" s="9" t="inlineStr"/>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>Branch.id</t>
-        </is>
-      </c>
-      <c r="H254" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I254" s="9" t="inlineStr"/>
-      <c r="J254" s="9" t="inlineStr"/>
-      <c r="K254" s="9" t="inlineStr">
-        <is>
-          <t>지점 ID</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>CodeSequence</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C255" s="9" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>CodeSequenceKind</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>enum CodeSequenceKind</t>
-        </is>
-      </c>
-      <c r="F255" s="9" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G255" s="9" t="inlineStr"/>
       <c r="H255" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I255" s="9" t="inlineStr"/>
+      <c r="I255" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
       <c r="J255" s="9" t="inlineStr"/>
       <c r="K255" s="9" t="inlineStr">
         <is>
-          <t>종류</t>
+          <t>식별자(UUID)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
         <is>
-          <t>CodeSequence</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C256" s="9" t="inlineStr">
         <is>
-          <t>prefix</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
@@ -12885,7 +12927,11 @@
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr"/>
-      <c r="G256" s="9" t="inlineStr"/>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>Branch.id</t>
+        </is>
+      </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
           <t>N</t>
@@ -12895,221 +12941,205 @@
       <c r="J256" s="9" t="inlineStr"/>
       <c r="K256" s="9" t="inlineStr">
         <is>
-          <t>코드 접두어</t>
+          <t>지점 ID</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>CodeSequence</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C257" s="9" t="inlineStr">
         <is>
-          <t>lastValue</t>
+          <t>requesterId</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr"/>
-      <c r="G257" s="9" t="inlineStr"/>
+      <c r="G257" s="9" t="inlineStr">
+        <is>
+          <t>Account.id</t>
+        </is>
+      </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I257" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I257" s="9" t="inlineStr"/>
       <c r="J257" s="9" t="inlineStr"/>
       <c r="K257" s="9" t="inlineStr">
         <is>
-          <t>마지막 발급 번호</t>
+          <t>FK → Account(지점 관리자)</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>MemberLinkAttempt</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="B258" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequestCategory</t>
+        </is>
+      </c>
+      <c r="E258" s="9" t="inlineStr">
+        <is>
+          <t>enum SupportRequestCategory</t>
+        </is>
+      </c>
+      <c r="F258" s="9" t="inlineStr"/>
+      <c r="G258" s="9" t="inlineStr"/>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I258" s="9" t="inlineStr"/>
+      <c r="J258" s="9" t="inlineStr"/>
+      <c r="K258" s="9" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="B259" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
+      <c r="E259" s="9" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F258" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G258" s="4" t="inlineStr"/>
-      <c r="H258" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="inlineStr">
-        <is>
-          <t>uuid()</t>
-        </is>
-      </c>
-      <c r="J258" s="4" t="inlineStr"/>
-      <c r="K258" s="4" t="inlineStr">
-        <is>
-          <t>식별자(UUID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>MemberLinkAttempt</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>memberNo</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
+      <c r="F259" s="9" t="inlineStr"/>
+      <c r="G259" s="9" t="inlineStr"/>
+      <c r="H259" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I259" s="9" t="inlineStr"/>
+      <c r="J259" s="9" t="inlineStr"/>
+      <c r="K259" s="9" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="E259" s="4" t="inlineStr">
+      <c r="E260" s="9" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F259" s="4" t="inlineStr"/>
-      <c r="G259" s="4" t="inlineStr"/>
-      <c r="H259" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I259" s="4" t="inlineStr"/>
-      <c r="J259" s="4" t="inlineStr"/>
-      <c r="K259" s="4" t="inlineStr">
-        <is>
-          <t>회원번호</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>MemberLinkAttempt</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="inlineStr">
-        <is>
-          <t>attemptedAt</t>
-        </is>
-      </c>
-      <c r="D260" s="4" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="E260" s="4" t="inlineStr">
-        <is>
-          <t>timestamp(3)</t>
-        </is>
-      </c>
-      <c r="F260" s="4" t="inlineStr"/>
-      <c r="G260" s="4" t="inlineStr"/>
-      <c r="H260" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I260" s="4" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J260" s="4" t="inlineStr"/>
-      <c r="K260" s="4" t="inlineStr">
-        <is>
-          <t>시도 일시</t>
+      <c r="F260" s="9" t="inlineStr"/>
+      <c r="G260" s="9" t="inlineStr"/>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I260" s="9" t="inlineStr"/>
+      <c r="J260" s="9" t="inlineStr"/>
+      <c r="K260" s="9" t="inlineStr">
+        <is>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C261" s="9" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>SupportRequestStatus</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F261" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>enum SupportRequestStatus</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr"/>
       <c r="G261" s="9" t="inlineStr"/>
       <c r="H261" s="9" t="inlineStr">
         <is>
@@ -13118,30 +13148,30 @@
       </c>
       <c r="I261" s="9" t="inlineStr">
         <is>
-          <t>uuid()</t>
+          <t>REQUESTED</t>
         </is>
       </c>
       <c r="J261" s="9" t="inlineStr"/>
       <c r="K261" s="9" t="inlineStr">
         <is>
-          <t>식별자(UUID)</t>
+          <t>상태(코드 정의 참고)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C262" s="9" t="inlineStr">
         <is>
-          <t>actorId</t>
+          <t>handlerId</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
@@ -13169,29 +13199,29 @@
       <c r="J262" s="9" t="inlineStr"/>
       <c r="K262" s="9" t="inlineStr">
         <is>
-          <t>행위자 계정 ID</t>
+          <t>FK → Account(마지막으로 상태를 바꾼 본사 관리자)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C263" s="9" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>response</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>String?</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
@@ -13203,82 +13233,82 @@
       <c r="G263" s="9" t="inlineStr"/>
       <c r="H263" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I263" s="9" t="inlineStr"/>
       <c r="J263" s="9" t="inlineStr"/>
       <c r="K263" s="9" t="inlineStr">
         <is>
-          <t>대상 테이블</t>
+          <t>본사 답변(반려 시 필수)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C264" s="9" t="inlineStr">
         <is>
-          <t>entityId</t>
+          <t>resolvedAt</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime?</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp(3)</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr"/>
       <c r="G264" s="9" t="inlineStr"/>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I264" s="9" t="inlineStr"/>
       <c r="J264" s="9" t="inlineStr"/>
       <c r="K264" s="9" t="inlineStr">
         <is>
-          <t>대상 레코드 ID</t>
+          <t>완료·반려 시각</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C265" s="9" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp(3)</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr"/>
@@ -13288,143 +13318,716 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I265" s="9" t="inlineStr"/>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J265" s="9" t="inlineStr"/>
       <c r="K265" s="9" t="inlineStr">
         <is>
-          <t>행위 — ROLE_CHANGED(역할 전환)·RESIGNED(퇴사)·ASSIGNED(파견 발령)·ASSIGNMENT_ENDED(계약 종료로 파견 종료)·PHONE_VIEWED(상세 전화번호 열람)</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
         <is>
-          <t>AuditLog</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="C266" s="9" t="inlineStr">
         <is>
-          <t>before</t>
+          <t>updatedAt</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Json?</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamp(3)</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr"/>
       <c r="G266" s="9" t="inlineStr"/>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I266" s="9" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I266" s="9" t="inlineStr">
+        <is>
+          <t>(수정 시 자동)</t>
+        </is>
+      </c>
       <c r="J266" s="9" t="inlineStr"/>
       <c r="K266" s="9" t="inlineStr">
         <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>branchId</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr"/>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>Branch.id</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr"/>
+      <c r="J267" s="4" t="inlineStr"/>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>지점 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequenceKind</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>enum CodeSequenceKind</t>
+        </is>
+      </c>
+      <c r="F268" s="4" t="inlineStr"/>
+      <c r="G268" s="4" t="inlineStr"/>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr"/>
+      <c r="J268" s="4" t="inlineStr"/>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr"/>
+      <c r="G269" s="4" t="inlineStr"/>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr"/>
+      <c r="J269" s="4" t="inlineStr"/>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>코드 접두어</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>lastValue</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="F270" s="4" t="inlineStr"/>
+      <c r="G270" s="4" t="inlineStr"/>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="inlineStr"/>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>마지막 발급 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>MemberLinkAttempt</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E271" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G271" s="9" t="inlineStr"/>
+      <c r="H271" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I271" s="9" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
+      <c r="J271" s="9" t="inlineStr"/>
+      <c r="K271" s="9" t="inlineStr">
+        <is>
+          <t>식별자(UUID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B272" s="9" t="inlineStr">
+        <is>
+          <t>MemberLinkAttempt</t>
+        </is>
+      </c>
+      <c r="C272" s="9" t="inlineStr">
+        <is>
+          <t>memberNo</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E272" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F272" s="9" t="inlineStr"/>
+      <c r="G272" s="9" t="inlineStr"/>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I272" s="9" t="inlineStr"/>
+      <c r="J272" s="9" t="inlineStr"/>
+      <c r="K272" s="9" t="inlineStr">
+        <is>
+          <t>회원번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B273" s="9" t="inlineStr">
+        <is>
+          <t>MemberLinkAttempt</t>
+        </is>
+      </c>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>attemptedAt</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E273" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F273" s="9" t="inlineStr"/>
+      <c r="G273" s="9" t="inlineStr"/>
+      <c r="H273" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I273" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J273" s="9" t="inlineStr"/>
+      <c r="K273" s="9" t="inlineStr">
+        <is>
+          <t>시도 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr"/>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>uuid()</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="inlineStr"/>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>식별자(UUID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>actorId</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>String?</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr"/>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>Account.id</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr"/>
+      <c r="J275" s="4" t="inlineStr"/>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>행위자 계정 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F276" s="4" t="inlineStr"/>
+      <c r="G276" s="4" t="inlineStr"/>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr"/>
+      <c r="J276" s="4" t="inlineStr"/>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>대상 테이블</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>entityId</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+      <c r="G277" s="4" t="inlineStr"/>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr"/>
+      <c r="J277" s="4" t="inlineStr"/>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>대상 레코드 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F278" s="4" t="inlineStr"/>
+      <c r="G278" s="4" t="inlineStr"/>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr"/>
+      <c r="J278" s="4" t="inlineStr"/>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>행위 — ROLE_CHANGED(역할 전환)·RESIGNED(퇴사)·ASSIGNED(파견 발령)·ASSIGNMENT_ENDED(계약 종료로 파견 종료)·PHONE_VIEWED(상세 전화번호 열람)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>AuditLog</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>Json?</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F279" s="4" t="inlineStr"/>
+      <c r="G279" s="4" t="inlineStr"/>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr"/>
+      <c r="J279" s="4" t="inlineStr"/>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
           <t>변경 전(JSON)</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="9" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B267" s="9" t="inlineStr">
+      <c r="B280" s="4" t="inlineStr">
         <is>
           <t>AuditLog</t>
         </is>
       </c>
-      <c r="C267" s="9" t="inlineStr">
+      <c r="C280" s="4" t="inlineStr">
         <is>
           <t>after</t>
         </is>
       </c>
-      <c r="D267" s="9" t="inlineStr">
+      <c r="D280" s="4" t="inlineStr">
         <is>
           <t>Json?</t>
         </is>
       </c>
-      <c r="E267" s="9" t="inlineStr">
+      <c r="E280" s="4" t="inlineStr">
         <is>
           <t>jsonb</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr"/>
-      <c r="G267" s="9" t="inlineStr"/>
-      <c r="H267" s="9" t="inlineStr">
+      <c r="F280" s="4" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr"/>
+      <c r="H280" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I267" s="9" t="inlineStr"/>
-      <c r="J267" s="9" t="inlineStr"/>
-      <c r="K267" s="9" t="inlineStr">
+      <c r="I280" s="4" t="inlineStr"/>
+      <c r="J280" s="4" t="inlineStr"/>
+      <c r="K280" s="4" t="inlineStr">
         <is>
           <t>변경 후(JSON)</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="9" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B268" s="9" t="inlineStr">
+      <c r="B281" s="4" t="inlineStr">
         <is>
           <t>AuditLog</t>
         </is>
       </c>
-      <c r="C268" s="9" t="inlineStr">
+      <c r="C281" s="4" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="D268" s="9" t="inlineStr">
+      <c r="D281" s="4" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="E268" s="9" t="inlineStr">
+      <c r="E281" s="4" t="inlineStr">
         <is>
           <t>timestamp(3)</t>
         </is>
       </c>
-      <c r="F268" s="9" t="inlineStr"/>
-      <c r="G268" s="9" t="inlineStr"/>
-      <c r="H268" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I268" s="9" t="inlineStr">
+      <c r="F281" s="4" t="inlineStr"/>
+      <c r="G281" s="4" t="inlineStr"/>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="J268" s="9" t="inlineStr"/>
-      <c r="K268" s="9" t="inlineStr">
+      <c r="J281" s="4" t="inlineStr"/>
+      <c r="K281" s="4" t="inlineStr">
         <is>
           <t>생성 일시</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K268"/>
+  <autoFilter ref="A4:K281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13435,7 +14038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13845,103 +14448,103 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
+          <t>facilityId</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>제한(기본)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
           <t>authorId</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Restrict</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>author</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Attachment</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>postId</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Post</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>PostReadReceipt</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>postId</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Post</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>post</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>accountId</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>제한(기본)</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>account</t>
         </is>
       </c>
     </row>
@@ -13953,12 +14556,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>branchId</t>
+          <t>accountId</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Account</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -13968,7 +14571,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>account</t>
         </is>
       </c>
     </row>
@@ -13980,49 +14583,49 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>branchId</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>제한(기본)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>assignedStaffId</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>assignedStaff</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>CourseEnrollment</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>memberId</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Cascade</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>member</t>
         </is>
       </c>
     </row>
@@ -14034,49 +14637,49 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
+          <t>memberId</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>CourseEnrollment</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
           <t>programId</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>program</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>PTSession</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>memberId</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Cascade</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>member</t>
         </is>
       </c>
     </row>
@@ -14088,76 +14691,76 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>memberId</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>PTSession</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>programId</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>PTSessionLog</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>ptSessionId</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>PTSession</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>ptSession</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Instructor</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>branchId</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>제한(기본)</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>branch</t>
         </is>
       </c>
     </row>
@@ -14169,49 +14772,49 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>branchId</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>제한(기본)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Instructor</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>staffId</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Program</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>branchId</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>제한(기본)</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>branch</t>
         </is>
       </c>
     </row>
@@ -14223,12 +14826,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>facilityId</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -14238,7 +14841,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>branch</t>
         </is>
       </c>
     </row>
@@ -14250,103 +14853,103 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
+          <t>facilityId</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>제한(기본)</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
           <t>instructorId</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Instructor</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>instructor</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>ProgramScheduleTemplate</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>programId</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>ScheduleSlot</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>programId</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>program</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Reservation</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>memberId</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Cascade</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>member</t>
         </is>
       </c>
     </row>
@@ -14358,49 +14961,49 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>memberId</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Reservation</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>scheduleSlotId</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>ScheduleSlot</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>scheduleSlot</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>reservationId</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Reservation</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Cascade</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>reservation</t>
         </is>
       </c>
     </row>
@@ -14412,101 +15015,101 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
+          <t>reservationId</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Reservation</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>reservation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
           <t>memberId</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>member</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Facility</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>branchId</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>CongestionSnapshot</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>facilityId</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Facility</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>facility</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>FacilityCheckIn</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>facilityId</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Cascade</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -14520,74 +15123,74 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>facilityId</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>FacilityCheckIn</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
           <t>memberId</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Cascade</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>member</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>branchId</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>branch</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Document</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>branchId</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>제한(기본)</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
@@ -14601,22 +15204,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>relatedStaffId</t>
+          <t>branchId</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Restrict</t>
+          <t>제한(기본)</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>relatedStaff</t>
+          <t>branch</t>
         </is>
       </c>
     </row>
@@ -14628,74 +15231,182 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>relatedStaffId</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Restrict</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>relatedStaff</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>uploadedBy</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Restrict</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>uploader</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>branchId</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>제한(기본)</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>requesterId</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Restrict</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>requester</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>handlerId</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Restrict</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>CodeSequence</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>branchId</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>AuditLog</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>actorId</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>제한(기본)</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
@@ -14712,7 +15423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16808,67 +17519,306 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>CodeSequenceKind</t>
+          <t>SupportRequestCategory</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>STAFF</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>FACILITY</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>CodeSequence.kind</t>
+          <t>SupportRequest.category</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>CodeSequenceKind</t>
+          <t>SupportRequestCategory</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>업무지원 요청</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>MEMBER</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr"/>
+          <t>STAFFING</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>인력</t>
+        </is>
+      </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>CodeSequence.kind</t>
+          <t>SupportRequest.category</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>SupportRequestCategory</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>SUPPLIES</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>물품</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>SupportRequest.category</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>SupportRequestCategory</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>전산</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>SupportRequest.category</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>SupportRequestCategory</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>SupportRequest.category</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequestStatus</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>REQUESTED</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequestStatus</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>처리중</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequestStatus</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequestStatus</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>업무지원 요청</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>반려(답변 필수)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
           <t>CodeSequenceKind</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>STAFF</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence.kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequenceKind</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence.kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequenceKind</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>ASSET</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr"/>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>CodeSequence.kind</t>
         </is>
@@ -16885,7 +17835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18170,17 +19120,17 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>CodeSequence</t>
+          <t>SupportRequest</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>기본키(복합)</t>
+          <t>인덱스</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>branchId,kind,prefix</t>
+          <t>branchId,status</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr"/>
@@ -18191,46 +19141,92 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>인덱스</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>status,createdAt</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr"/>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>스키마</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>CodeSequence</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>기본키(복합)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>branchId,kind,prefix</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>스키마</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>MemberLinkAttempt</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>인덱스</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>memberNo,attemptedAt</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>스키마</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>AuditLog</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>인덱스</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>entity,entityId</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>스키마</t>
         </is>
@@ -18247,7 +19243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18274,7 +19270,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>CHECK 제약 18개</t>
+          <t>CHECK 제약 20개</t>
         </is>
       </c>
     </row>
@@ -18791,113 +19787,113 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest_rejected_response_ck</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>status &lt;&gt; 'REJECTED' OR (response IS NOT NULL AND length(btrim(response)) &gt; 0)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>D56 — 한 행 안에서 판정 가능한 상태 규칙을 CHECK로 이중화한다(D28과 같은 방식, schema.prisma에는 표현되지 않는다). 반려에는 답변이 있어야 하고, 완료·반려일 때만 처리 시각이 있다.</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>20261017031420_d56_support_request</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>지점 일치 트리거 7개 — 연결된 데이터는 같은 지점이어야 한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>SupportRequest_resolved_at_ck</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>(status IN ('DONE', 'REJECTED')) = (resolvedAt IS NOT NULL)</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>D56 — 한 행 안에서 판정 가능한 상태 규칙을 CHECK로 이중화한다(D28과 같은 방식, schema.prisma에는 표현되지 않는다). 반려에는 답변이 있어야 하고, 완료·반려일 때만 처리 시각이 있다.</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>20261017031420_d56_support_request</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>지점 일치 트리거 8개 — 연결된 데이터는 같은 지점이어야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>트리거명</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>시점·대상</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>마이그레이션</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Program</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>program_branch_consistency</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>BEFORE INSERT OR UPDATE OF branchId, facilityId, instructorId</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ADR-PRG-03(assertFacilityInBranch·assertInstructorInBranch): 프로그램의 시설·강사는 같은 지점</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>20260929005902_d28_branch_consistency_triggers</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>member_assigned_staff_branch</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>BEFORE INSERT OR UPDATE OF branchId, assignedStaffId</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>MEM-T02(assertStaffInBranch): 회원의 담당 직원은 같은 지점</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>CourseEnrollment</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>course_enrollment_branch</t>
+          <t>program_branch_consistency</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>BEFORE INSERT OR UPDATE OF memberId, programId</t>
+          <t>BEFORE INSERT OR UPDATE OF branchId, facilityId, instructorId</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>ADR-MEM-03(assertProgramInBranch): 수강·PT 세션의 프로그램은 회원과 같은 지점 — 두 테이블이 같은 함수를 쓴다</t>
+          <t>ADR-PRG-03(assertFacilityInBranch·assertInstructorInBranch): 프로그램의 시설·강사는 같은 지점</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -18909,22 +19905,22 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PTSession</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>pt_session_branch</t>
+          <t>member_assigned_staff_branch</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>BEFORE INSERT OR UPDATE OF memberId, programId</t>
+          <t>BEFORE INSERT OR UPDATE OF branchId, assignedStaffId</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>ADR-MEM-03(assertProgramInBranch): 수강·PT 세션의 프로그램은 회원과 같은 지점 — 두 테이블이 같은 함수를 쓴다</t>
+          <t>MEM-T02(assertStaffInBranch): 회원의 담당 직원은 같은 지점</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -18936,22 +19932,22 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Reservation</t>
+          <t>CourseEnrollment</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>reservation_branch</t>
+          <t>course_enrollment_branch</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>BEFORE INSERT OR UPDATE OF memberId, scheduleSlotId</t>
+          <t>BEFORE INSERT OR UPDATE OF memberId, programId</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>DI-02에서 발견한 공백(createReservation MEMBER_BRANCH_MISMATCH): 예약 회차의 프로그램은 회원과 같은 지점</t>
+          <t>ADR-MEM-03(assertProgramInBranch): 수강·PT 세션의 프로그램은 회원과 같은 지점 — 두 테이블이 같은 함수를 쓴다</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -18963,22 +19959,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Instructor</t>
+          <t>PTSession</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>instructor_staff_branch</t>
+          <t>pt_session_branch</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>BEFORE INSERT OR UPDATE OF branchId, staffId</t>
+          <t>BEFORE INSERT OR UPDATE OF memberId, programId</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ADR-STF-04: 강사 프로필에 연결된 직원은 같은 지점(파견 시 연결을 해제해야 한다)</t>
+          <t>ADR-MEM-03(assertProgramInBranch): 수강·PT 세션의 프로그램은 회원과 같은 지점 — 두 테이블이 같은 함수를 쓴다</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -18990,27 +19986,108 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
+          <t>Reservation</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>reservation_branch</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>BEFORE INSERT OR UPDATE OF memberId, scheduleSlotId</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>DI-02에서 발견한 공백(createReservation MEMBER_BRANCH_MISMATCH): 예약 회차의 프로그램은 회원과 같은 지점</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>20260929005902_d28_branch_consistency_triggers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Instructor</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>instructor_staff_branch</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>BEFORE INSERT OR UPDATE OF branchId, staffId</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ADR-STF-04: 강사 프로필에 연결된 직원은 같은 지점(파견 시 연결을 해제해야 한다)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>20260929005902_d28_branch_consistency_triggers</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>staff_branch_move</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>BEFORE UPDATE OF branchId</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>ADR-STF-04 A안을 DB가 강제한다 — 담당 회원 해제·강사 프로필 연결 해제를 같은 트랜잭션에서 **먼저** 하지 않으면 Staff.branchId 갱신이 거부된다. (Facility·Instructor·Program의 branchId를 바꾸는 경로는 앱에 없어 역방향은 두지 않았다.)</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>post_facility_branch</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>BEFORE INSERT OR UPDATE OF branchId, facilityId</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>D28 DI-02 방식 — 공지의 시설은 공지와 같은 지점(전체 공지 branchId=null에는 시설을 둘 수 없다). 앱이 먼저 403/400을 내고(BranchScopeGuard·PostService), 트리거는 최종 방어선이다.</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>20261020120300_f43_post_facility</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/데이터정의서.xlsx
+++ b/docs/deliverables/데이터정의서.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB 규칙" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'컬럼 정의'!$A$4:$K$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'컬럼 정의'!$A$4:$K$293</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -595,7 +595,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>테이블 32개 · 컬럼 277개 · 코드(enum) 26종 · CHECK 20개 · 트리거 8개</t>
+          <t>테이블 34개 · 컬럼 289개 · 코드(enum) 27종 · CHECK 21개 · 트리거 8개</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>읽음 확인(PostReadReceipt), 프로그램 시간표 틀(ProgramScheduleTemplate), 혼잡도 기록(CongestionSnapshot), 시설 입퇴장(FacilityCheckIn) — 스키마에만 있고 코드가 읽거나 쓰지 않는다. 사유는 테이블 목록의 설명(요구사항 정의서 "미구현"·"범위 제외" 탭)</t>
+          <t>읽음 확인(PostReadReceipt), 프로그램 시간표 틀(ProgramScheduleTemplate), 혼잡도 기록(CongestionSnapshot), 시설 입퇴장(FacilityCheckIn), 개인 예외 권한(AccountPermission) — 스키마에만 있고 코드가 읽거나 쓰지 않는다. 사유는 테이블 목록의 설명(요구사항 정의서 "미구현"·"범위 제외" 탭)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1853,13 +1853,81 @@
       </c>
     </row>
     <row r="37">
-      <c r="E37" s="8" t="inlineStr">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>역할 기본 권한</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>지점 관리자·직원의 기능×동작(조회·입력·수정·삭제·출력) 권한 중 기본값에서 바꾼 칸(D60). 행이 없으면 역할 상한대로 허용</t>
+        </is>
+      </c>
+      <c r="F37" s="4">
+        <f>COUNTIF('컬럼 정의'!$B:$B,C37)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>개인 예외 권한</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>한 사람의 기능×동작 권한을 역할 기본값과 다르게 허용·차단(D60). 역할 상한은 넘지 못한다</t>
+        </is>
+      </c>
+      <c r="F38" s="4">
+        <f>COUNTIF('컬럼 정의'!$B:$B,C38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>미사용(설계만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="F37" s="8">
-        <f>SUM(F5:F36)</f>
+      <c r="F39" s="8">
+        <f>SUM(F5:F38)</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K281"/>
+  <dimension ref="A1:K293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14026,8 +14094,492 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B282" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="C282" s="9" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E282" s="9" t="inlineStr">
+        <is>
+          <t>enum Role</t>
+        </is>
+      </c>
+      <c r="F282" s="9" t="inlineStr"/>
+      <c r="G282" s="9" t="inlineStr"/>
+      <c r="H282" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I282" s="9" t="inlineStr"/>
+      <c r="J282" s="9" t="inlineStr"/>
+      <c r="K282" s="9" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="C283" s="9" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E283" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F283" s="9" t="inlineStr"/>
+      <c r="G283" s="9" t="inlineStr"/>
+      <c r="H283" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I283" s="9" t="inlineStr"/>
+      <c r="J283" s="9" t="inlineStr"/>
+      <c r="K283" s="9" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="C284" s="9" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="E284" s="9" t="inlineStr">
+        <is>
+          <t>enum PermissionAction</t>
+        </is>
+      </c>
+      <c r="F284" s="9" t="inlineStr"/>
+      <c r="G284" s="9" t="inlineStr"/>
+      <c r="H284" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I284" s="9" t="inlineStr"/>
+      <c r="J284" s="9" t="inlineStr"/>
+      <c r="K284" s="9" t="inlineStr">
+        <is>
+          <t>행위 — ROLE_CHANGED(역할 전환)·RESIGNED(퇴사)·ASSIGNED(파견 발령)·ASSIGNMENT_ENDED(계약 종료로 파견 종료)·PHONE_VIEWED(상세 전화번호 열람)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>allowed</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F285" s="9" t="inlineStr"/>
+      <c r="G285" s="9" t="inlineStr"/>
+      <c r="H285" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I285" s="9" t="inlineStr"/>
+      <c r="J285" s="9" t="inlineStr"/>
+      <c r="K285" s="9" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B286" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="C286" s="9" t="inlineStr">
+        <is>
+          <t>updatedBy</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>String?</t>
+        </is>
+      </c>
+      <c r="E286" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F286" s="9" t="inlineStr"/>
+      <c r="G286" s="9" t="inlineStr"/>
+      <c r="H286" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I286" s="9" t="inlineStr"/>
+      <c r="J286" s="9" t="inlineStr"/>
+      <c r="K286" s="9" t="inlineStr">
+        <is>
+          <t>바꾼 본사 계정(변경 이력은 AuditLog PERMISSION_CHANGED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B287" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E287" s="9" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F287" s="9" t="inlineStr"/>
+      <c r="G287" s="9" t="inlineStr"/>
+      <c r="H287" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I287" s="9" t="inlineStr">
+        <is>
+          <t>(수정 시 자동)</t>
+        </is>
+      </c>
+      <c r="J287" s="9" t="inlineStr"/>
+      <c r="K287" s="9" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>accountId</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F288" s="4" t="inlineStr"/>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>Account.id</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr"/>
+      <c r="J288" s="4" t="inlineStr"/>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>계정 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F289" s="4" t="inlineStr"/>
+      <c r="G289" s="4" t="inlineStr"/>
+      <c r="H289" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I289" s="4" t="inlineStr"/>
+      <c r="J289" s="4" t="inlineStr"/>
+      <c r="K289" s="4" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>enum PermissionAction</t>
+        </is>
+      </c>
+      <c r="F290" s="4" t="inlineStr"/>
+      <c r="G290" s="4" t="inlineStr"/>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I290" s="4" t="inlineStr"/>
+      <c r="J290" s="4" t="inlineStr"/>
+      <c r="K290" s="4" t="inlineStr">
+        <is>
+          <t>행위 — ROLE_CHANGED(역할 전환)·RESIGNED(퇴사)·ASSIGNED(파견 발령)·ASSIGNMENT_ENDED(계약 종료로 파견 종료)·PHONE_VIEWED(상세 전화번호 열람)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>allowed</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F291" s="4" t="inlineStr"/>
+      <c r="G291" s="4" t="inlineStr"/>
+      <c r="H291" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr"/>
+      <c r="J291" s="4" t="inlineStr"/>
+      <c r="K291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>grantedBy</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F292" s="4" t="inlineStr"/>
+      <c r="G292" s="4" t="inlineStr"/>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr"/>
+      <c r="J292" s="4" t="inlineStr"/>
+      <c r="K292" s="4" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="D293" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>timestamp(3)</t>
+        </is>
+      </c>
+      <c r="F293" s="4" t="inlineStr"/>
+      <c r="G293" s="4" t="inlineStr"/>
+      <c r="H293" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I293" s="4" t="inlineStr">
+        <is>
+          <t>(수정 시 자동)</t>
+        </is>
+      </c>
+      <c r="J293" s="4" t="inlineStr"/>
+      <c r="K293" s="4" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K281"/>
+  <autoFilter ref="A4:K293"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14038,7 +14590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15412,6 +15964,33 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>accountId</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15423,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15493,7 +16072,7 @@
       <c r="D5" s="9" t="inlineStr"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Account.role</t>
+          <t>Account.role, RolePermission.role</t>
         </is>
       </c>
     </row>
@@ -15516,7 +16095,7 @@
       <c r="D6" s="9" t="inlineStr"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Account.role</t>
+          <t>Account.role, RolePermission.role</t>
         </is>
       </c>
     </row>
@@ -15543,7 +16122,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Account.role</t>
+          <t>Account.role, RolePermission.role</t>
         </is>
       </c>
     </row>
@@ -15566,7 +16145,7 @@
       <c r="D8" s="9" t="inlineStr"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Account.role</t>
+          <t>Account.role, RolePermission.role</t>
         </is>
       </c>
     </row>
@@ -17821,6 +18400,121 @@
       <c r="E98" s="4" t="inlineStr">
         <is>
           <t>CodeSequence.kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr"/>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission.action, AccountPermission.action</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission.action, AccountPermission.action</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>UPDATE</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr"/>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission.action, AccountPermission.action</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission.action, AccountPermission.action</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>PermissionAction</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>EXPORT</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr"/>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission.action, AccountPermission.action</t>
         </is>
       </c>
     </row>
@@ -17835,7 +18529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19232,6 +19926,52 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>기본키(복합)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>role,feature,action</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>스키마</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>AccountPermission</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>기본키(복합)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>accountId,feature,action</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>스키마</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19243,7 +19983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19270,7 +20010,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>CHECK 제약 20개</t>
+          <t>CHECK 제약 21개</t>
         </is>
       </c>
     </row>
@@ -19841,251 +20581,278 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>RolePermission</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>RolePermission_role_check</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>role IN ('BRANCH_ADMIN', 'STAFF')</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>세부 권한 표는 지점 관리자·직원만 다룬다(본사는 항상 전부, 회원은 본인 화면만 — D60 결정 2).</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>20261020135659_d60_permission_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>지점 일치 트리거 8개 — 연결된 데이터는 같은 지점이어야 한다</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>트리거명</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>시점·대상</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>마이그레이션</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>program_branch_consistency</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF branchId, facilityId, instructorId</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>ADR-PRG-03(assertFacilityInBranch·assertInstructorInBranch): 프로그램의 시설·강사는 같은 지점</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>member_assigned_staff_branch</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF branchId, assignedStaffId</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>MEM-T02(assertStaffInBranch): 회원의 담당 직원은 같은 지점</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>CourseEnrollment</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>course_enrollment_branch</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF memberId, programId</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>ADR-MEM-03(assertProgramInBranch): 수강·PT 세션의 프로그램은 회원과 같은 지점 — 두 테이블이 같은 함수를 쓴다</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>PTSession</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>pt_session_branch</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF memberId, programId</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>ADR-MEM-03(assertProgramInBranch): 수강·PT 세션의 프로그램은 회원과 같은 지점 — 두 테이블이 같은 함수를 쓴다</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Reservation</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>reservation_branch</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF memberId, scheduleSlotId</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>DI-02에서 발견한 공백(createReservation MEMBER_BRANCH_MISMATCH): 예약 회차의 프로그램은 회원과 같은 지점</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Instructor</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>instructor_staff_branch</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF branchId, staffId</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>ADR-STF-04: 강사 프로필에 연결된 직원은 같은 지점(파견 시 연결을 해제해야 한다)</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>staff_branch_move</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>BEFORE UPDATE OF branchId</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>ADR-STF-04 A안을 DB가 강제한다 — 담당 회원 해제·강사 프로필 연결 해제를 같은 트랜잭션에서 **먼저** 하지 않으면 Staff.branchId 갱신이 거부된다. (Facility·Instructor·Program의 branchId를 바꾸는 경로는 앱에 없어 역방향은 두지 않았다.)</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>20260929005902_d28_branch_consistency_triggers</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Post</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>post_facility_branch</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>BEFORE INSERT OR UPDATE OF branchId, facilityId</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>D28 DI-02 방식 — 공지의 시설은 공지와 같은 지점(전체 공지 branchId=null에는 시설을 둘 수 없다). 앱이 먼저 403/400을 내고(BranchScopeGuard·PostService), 트리거는 최종 방어선이다.</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>20261020120300_f43_post_facility</t>
         </is>
